--- a/salles/SALLE PRINCIPALE.xlsx
+++ b/salles/SALLE PRINCIPALE.xlsx
@@ -630,7 +630,7 @@
       <c r="L3" s="30" t="n"/>
       <c r="M3" s="16" t="inlineStr">
         <is>
-          <t>11H - 13H30</t>
+          <t>13H30 - 16H30</t>
         </is>
       </c>
       <c r="N3" s="15" t="inlineStr">
